--- a/input/api_definition.xlsx
+++ b/input/api_definition.xlsx
@@ -96,7 +96,7 @@
     <t>名前: 値（改行区切り）</t>
   </si>
   <si>
-    <t>auto / json / form / raw</t>
+    <t>auto / json / form / raw / xml / multipart</t>
   </si>
   <si>
     <t>JSON 等 / 名前=値</t>
@@ -990,7 +990,7 @@
     <t>○</t>
   </si>
   <si>
-    <t>HTTP メソッド（GET / POST。PUT / PATCH / DELETE も可）</t>
+    <t>HTTP メソッド（GET / POST / PUT / PATCH / DELETE / HEAD / OPTIONS / TRACE）</t>
   </si>
   <si>
     <t>完全な URL、またはベースURL 設定時は「/」で始まるパス。${変数} 可。? 以降のクエリも可</t>
@@ -1009,10 +1009,10 @@
     <t>この API だけに付けるヘッダ（全 API 共通のヘッダは設定 common_headers）</t>
   </si>
   <si>
-    <t>リクエストボディの形式。空欄 = auto（自動判定）</t>
-  </si>
-  <si>
-    <t>POST 等で送る本文。form 形式は「名前=値」を改行 / &amp; 区切り</t>
+    <t>リクエストボディの形式（auto / json / form / raw / xml / multipart）。空欄 = auto（自動判定）</t>
+  </si>
+  <si>
+    <t>POST 等で送る本文（前後の空白・改行も含めてそのまま送信）。form / multipart 形式は「名前=値」を改行 / &amp; 区切り</t>
   </si>
   <si>
     <t>{"userId":"${USER_ID}"}</t>
@@ -1636,7 +1636,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" ht="46.8" customHeight="1">
+    <row r="4" ht="61.2" customHeight="1">
       <c r="A4" s="19" t="s">
         <v>20</v>
       </c>
@@ -2298,10 +2298,10 @@
       <formula1>"Y,N"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="D5:D300">
-      <formula1>"GET,POST,PUT,PATCH,DELETE"</formula1>
+      <formula1>"GET,POST,PUT,PATCH,DELETE,HEAD,OPTIONS,TRACE"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" sqref="H5:H300">
-      <formula1>"auto,json,form,raw"</formula1>
+      <formula1>"auto,json,form,raw,xml,multipart"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
@@ -3716,7 +3716,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="29" ht="18" customHeight="1">
+    <row r="29" ht="32.4" customHeight="1">
       <c r="B29" s="15" t="s">
         <v>5</v>
       </c>
@@ -3768,7 +3768,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="33" ht="18" customHeight="1">
+    <row r="33" ht="32.4" customHeight="1">
       <c r="B33" s="15" t="s">
         <v>9</v>
       </c>
@@ -3780,7 +3780,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="34" ht="18" customHeight="1">
+    <row r="34" ht="32.4" customHeight="1">
       <c r="B34" s="14" t="s">
         <v>10</v>
       </c>
